--- a/esp32_divider.xlsx
+++ b/esp32_divider.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\privat\penplotter_04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B699DD2-CBFF-46B5-8F12-0771D1240017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC4CD6F7-812F-4EAC-AC8C-9B7293C43B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2250" yWindow="1020" windowWidth="26670" windowHeight="14460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t>internal clock (mhz)</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>frq</t>
+  </si>
+  <si>
+    <t>planar.r</t>
   </si>
 </sst>
 </file>
@@ -454,10 +457,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:Y42"/>
+  <dimension ref="B2:Y69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19.28515625" customWidth="1"/>
+    <col min="3" max="3" width="36.42578125" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="3.85546875" customWidth="1"/>
     <col min="6" max="8" width="6.28515625" customWidth="1"/>
@@ -1660,6 +1664,17 @@
       </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B36">
+        <f>(200*8*1000*30/18)</f>
+        <v>2666666.6666666665</v>
+      </c>
+      <c r="C36">
+        <v>2666666</v>
+      </c>
+      <c r="D36">
+        <f>$B$36/C36</f>
+        <v>1.0000002500000624</v>
+      </c>
       <c r="F36" t="s">
         <v>11</v>
       </c>
@@ -1686,6 +1701,14 @@
       </c>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C37">
+        <f>C36+1</f>
+        <v>2666667</v>
+      </c>
+      <c r="D37">
+        <f>$B$36/C37</f>
+        <v>0.99999987500001553</v>
+      </c>
       <c r="F37">
         <v>0</v>
       </c>
@@ -1716,6 +1739,14 @@
       </c>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C38">
+        <f t="shared" ref="C38:C69" si="72">C37+1</f>
+        <v>2666668</v>
+      </c>
+      <c r="D38">
+        <f t="shared" ref="D38:D54" si="73">$B$36/C38</f>
+        <v>0.99999950000024995</v>
+      </c>
       <c r="F38">
         <v>1</v>
       </c>
@@ -1729,23 +1760,31 @@
         <v>2</v>
       </c>
       <c r="J38">
-        <f t="shared" ref="J38:J42" si="72">400*I38</f>
+        <f t="shared" ref="J38:J42" si="74">400*I38</f>
         <v>800</v>
       </c>
       <c r="K38">
-        <f t="shared" ref="K38:K42" si="73">40/J38</f>
+        <f t="shared" ref="K38:K42" si="75">40/J38</f>
         <v>0.05</v>
       </c>
       <c r="L38">
-        <f t="shared" ref="L38:L42" si="74">1/K38</f>
+        <f t="shared" ref="L38:L42" si="76">1/K38</f>
         <v>20</v>
       </c>
       <c r="M38">
-        <f t="shared" ref="M38:M42" si="75">L38*420</f>
+        <f t="shared" ref="M38:M42" si="77">L38*420</f>
         <v>8400</v>
       </c>
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C39">
+        <f t="shared" si="72"/>
+        <v>2666669</v>
+      </c>
+      <c r="D39">
+        <f t="shared" si="73"/>
+        <v>0.9999991250007656</v>
+      </c>
       <c r="F39">
         <v>0</v>
       </c>
@@ -1759,23 +1798,31 @@
         <v>4</v>
       </c>
       <c r="J39">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>1600</v>
       </c>
       <c r="K39">
+        <f t="shared" si="75"/>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="L39">
+        <f t="shared" si="76"/>
+        <v>40</v>
+      </c>
+      <c r="M39">
+        <f t="shared" si="77"/>
+        <v>16800</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C40">
+        <f t="shared" si="72"/>
+        <v>2666670</v>
+      </c>
+      <c r="D40">
         <f t="shared" si="73"/>
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="L39">
-        <f t="shared" si="74"/>
-        <v>40</v>
-      </c>
-      <c r="M39">
-        <f t="shared" si="75"/>
-        <v>16800</v>
-      </c>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
+        <v>0.99999875000156246</v>
+      </c>
       <c r="F40">
         <v>1</v>
       </c>
@@ -1789,23 +1836,31 @@
         <v>8</v>
       </c>
       <c r="J40">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>3200</v>
       </c>
       <c r="K40">
+        <f t="shared" si="75"/>
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="L40">
+        <f t="shared" si="76"/>
+        <v>80</v>
+      </c>
+      <c r="M40">
+        <f t="shared" si="77"/>
+        <v>33600</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C41">
+        <f t="shared" si="72"/>
+        <v>2666671</v>
+      </c>
+      <c r="D41">
         <f t="shared" si="73"/>
-        <v>1.2500000000000001E-2</v>
-      </c>
-      <c r="L40">
-        <f t="shared" si="74"/>
-        <v>80</v>
-      </c>
-      <c r="M40">
-        <f t="shared" si="75"/>
-        <v>33600</v>
-      </c>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
+        <v>0.99999837500264055</v>
+      </c>
       <c r="F41">
         <v>0</v>
       </c>
@@ -1819,23 +1874,31 @@
         <v>16</v>
       </c>
       <c r="J41">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>6400</v>
       </c>
       <c r="K41">
+        <f t="shared" si="75"/>
+        <v>6.2500000000000003E-3</v>
+      </c>
+      <c r="L41">
+        <f t="shared" si="76"/>
+        <v>160</v>
+      </c>
+      <c r="M41">
+        <f t="shared" si="77"/>
+        <v>67200</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C42">
+        <f t="shared" si="72"/>
+        <v>2666672</v>
+      </c>
+      <c r="D42">
         <f t="shared" si="73"/>
-        <v>6.2500000000000003E-3</v>
-      </c>
-      <c r="L41">
-        <f t="shared" si="74"/>
-        <v>160</v>
-      </c>
-      <c r="M41">
-        <f t="shared" si="75"/>
-        <v>67200</v>
-      </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
+        <v>0.99999800000399997</v>
+      </c>
       <c r="F42">
         <v>1</v>
       </c>
@@ -1849,20 +1912,300 @@
         <v>32</v>
       </c>
       <c r="J42">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>12800</v>
       </c>
       <c r="K42">
+        <f t="shared" si="75"/>
+        <v>3.1250000000000002E-3</v>
+      </c>
+      <c r="L42">
+        <f t="shared" si="76"/>
+        <v>320</v>
+      </c>
+      <c r="M42">
+        <f t="shared" si="77"/>
+        <v>134400</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C43">
+        <f t="shared" si="72"/>
+        <v>2666673</v>
+      </c>
+      <c r="D43">
         <f t="shared" si="73"/>
-        <v>3.1250000000000002E-3</v>
-      </c>
-      <c r="L42">
-        <f t="shared" si="74"/>
-        <v>320</v>
-      </c>
-      <c r="M42">
-        <f t="shared" si="75"/>
-        <v>134400</v>
+        <v>0.9999976250056406</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C44">
+        <f t="shared" si="72"/>
+        <v>2666674</v>
+      </c>
+      <c r="D44">
+        <f t="shared" si="73"/>
+        <v>0.99999725000756245</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C45">
+        <f t="shared" si="72"/>
+        <v>2666675</v>
+      </c>
+      <c r="D45">
+        <f t="shared" si="73"/>
+        <v>0.99999687500976553</v>
+      </c>
+      <c r="I45" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C46">
+        <f t="shared" si="72"/>
+        <v>2666676</v>
+      </c>
+      <c r="D46">
+        <f t="shared" si="73"/>
+        <v>0.99999650001224993</v>
+      </c>
+      <c r="I46">
+        <v>600</v>
+      </c>
+      <c r="J46">
+        <f>I46*1000</f>
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C47">
+        <f t="shared" si="72"/>
+        <v>2666677</v>
+      </c>
+      <c r="D47">
+        <f t="shared" si="73"/>
+        <v>0.99999612501501556</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C48">
+        <f t="shared" si="72"/>
+        <v>2666678</v>
+      </c>
+      <c r="D48">
+        <f t="shared" si="73"/>
+        <v>0.9999957500180624</v>
+      </c>
+    </row>
+    <row r="49" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C49">
+        <f t="shared" si="72"/>
+        <v>2666679</v>
+      </c>
+      <c r="D49">
+        <f t="shared" si="73"/>
+        <v>0.99999537502139046</v>
+      </c>
+    </row>
+    <row r="50" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C50">
+        <f t="shared" si="72"/>
+        <v>2666680</v>
+      </c>
+      <c r="D50">
+        <f t="shared" si="73"/>
+        <v>0.99999500002499986</v>
+      </c>
+    </row>
+    <row r="51" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C51">
+        <f t="shared" si="72"/>
+        <v>2666681</v>
+      </c>
+      <c r="D51">
+        <f t="shared" si="73"/>
+        <v>0.99999462502889036</v>
+      </c>
+    </row>
+    <row r="52" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C52">
+        <f t="shared" si="72"/>
+        <v>2666682</v>
+      </c>
+      <c r="D52">
+        <f t="shared" si="73"/>
+        <v>0.9999942500330623</v>
+      </c>
+    </row>
+    <row r="53" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C53">
+        <f t="shared" si="72"/>
+        <v>2666683</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="73"/>
+        <v>0.99999387503751536</v>
+      </c>
+    </row>
+    <row r="54" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C54">
+        <f t="shared" si="72"/>
+        <v>2666684</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="73"/>
+        <v>0.99999350004224963</v>
+      </c>
+    </row>
+    <row r="55" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C55">
+        <f t="shared" si="72"/>
+        <v>2666685</v>
+      </c>
+      <c r="D55">
+        <f>$B$36/C55</f>
+        <v>0.99999312504726523</v>
+      </c>
+    </row>
+    <row r="56" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C56">
+        <f t="shared" si="72"/>
+        <v>2666686</v>
+      </c>
+      <c r="D56">
+        <f>$B$36/C56</f>
+        <v>0.99999275005256205</v>
+      </c>
+    </row>
+    <row r="57" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C57">
+        <f t="shared" si="72"/>
+        <v>2666687</v>
+      </c>
+      <c r="D57">
+        <f t="shared" ref="D57:D69" si="78">$B$36/C57</f>
+        <v>0.99999237505814009</v>
+      </c>
+    </row>
+    <row r="58" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C58">
+        <f t="shared" si="72"/>
+        <v>2666688</v>
+      </c>
+      <c r="D58">
+        <f t="shared" si="78"/>
+        <v>0.99999200006399946</v>
+      </c>
+    </row>
+    <row r="59" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C59">
+        <f t="shared" si="72"/>
+        <v>2666689</v>
+      </c>
+      <c r="D59">
+        <f t="shared" si="78"/>
+        <v>0.99999162507013994</v>
+      </c>
+    </row>
+    <row r="60" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C60">
+        <f t="shared" si="72"/>
+        <v>2666690</v>
+      </c>
+      <c r="D60">
+        <f t="shared" si="78"/>
+        <v>0.99999125007656176</v>
+      </c>
+    </row>
+    <row r="61" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C61">
+        <f t="shared" si="72"/>
+        <v>2666691</v>
+      </c>
+      <c r="D61">
+        <f t="shared" si="78"/>
+        <v>0.99999087508326479</v>
+      </c>
+    </row>
+    <row r="62" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C62">
+        <f t="shared" si="72"/>
+        <v>2666692</v>
+      </c>
+      <c r="D62">
+        <f t="shared" si="78"/>
+        <v>0.99999050009024903</v>
+      </c>
+    </row>
+    <row r="63" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C63">
+        <f t="shared" si="72"/>
+        <v>2666693</v>
+      </c>
+      <c r="D63">
+        <f t="shared" si="78"/>
+        <v>0.99999012509751461</v>
+      </c>
+    </row>
+    <row r="64" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C64">
+        <f t="shared" si="72"/>
+        <v>2666694</v>
+      </c>
+      <c r="D64">
+        <f t="shared" si="78"/>
+        <v>0.99998975010506141</v>
+      </c>
+    </row>
+    <row r="65" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C65">
+        <f t="shared" si="72"/>
+        <v>2666695</v>
+      </c>
+      <c r="D65">
+        <f t="shared" si="78"/>
+        <v>0.99998937511288932</v>
+      </c>
+    </row>
+    <row r="66" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C66">
+        <f t="shared" si="72"/>
+        <v>2666696</v>
+      </c>
+      <c r="D66">
+        <f t="shared" si="78"/>
+        <v>0.99998900012099856</v>
+      </c>
+    </row>
+    <row r="67" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C67">
+        <f t="shared" si="72"/>
+        <v>2666697</v>
+      </c>
+      <c r="D67">
+        <f t="shared" si="78"/>
+        <v>0.99998862512938913</v>
+      </c>
+    </row>
+    <row r="68" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C68">
+        <f t="shared" si="72"/>
+        <v>2666698</v>
+      </c>
+      <c r="D68">
+        <f t="shared" si="78"/>
+        <v>0.99998825013806081</v>
+      </c>
+    </row>
+    <row r="69" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C69">
+        <f t="shared" si="72"/>
+        <v>2666699</v>
+      </c>
+      <c r="D69">
+        <f t="shared" si="78"/>
+        <v>0.99998787514701382</v>
       </c>
     </row>
   </sheetData>
